--- a/samples/clover/design-data/xlsx/Cards.xlsx
+++ b/samples/clover/design-data/xlsx/Cards.xlsx
@@ -22,16 +22,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[BaseDeckCard!$B$2:$E$56]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[PokerHand!$B$2:$H$16]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[Enhancement!$B$2:$C$13]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1"><![CDATA[EnhancementEffect!$B$2:$BL$16]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1"><![CDATA[EnhancementEffect!$B$2:$BM$16]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1"><![CDATA[Seal!$B$2:$C$9]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1"><![CDATA[SealEffect!$B$2:$BL$8]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1"><![CDATA[SealEffect!$B$2:$BM$8]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1"><![CDATA[Edition!$B$2:$H$9]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="323">
   <si>
     <t xml:space="preserve">:table Rank(key=rank)</t>
   </si>
@@ -739,6 +739,9 @@
   </si>
   <si>
     <t xml:space="preserve">operation.handler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">operation.sticker</t>
   </si>
   <si>
     <t xml:space="preserve">int (min=0, max=15)</t>
@@ -2919,7 +2922,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:BL16"/>
+  <dimension ref="A1:BM16"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.734375" customWidth="1"/>
@@ -2970,7 +2973,7 @@
     <col min="59" max="60" width="23.4375" customWidth="1"/>
     <col min="61" max="61" width="18.75" customWidth="1"/>
     <col min="62" max="63" width="21.09375" customWidth="1"/>
-    <col min="64" max="64" width="22.265625" customWidth="1"/>
+    <col min="64" max="65" width="22.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3042,6 +3045,7 @@
       <c r="BJ1" s="2"/>
       <c r="BK1" s="2"/>
       <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -3236,6 +3240,9 @@
       <c r="BL2" s="4" t="s">
         <v>235</v>
       </c>
+      <c r="BM2" s="4" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -3245,34 +3252,34 @@
         <v>149</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>238</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -3289,7 +3296,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -3328,43 +3335,44 @@
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
+      <c r="BM3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -3381,7 +3389,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -3420,6 +3428,7 @@
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
+      <c r="BM4" s="4"/>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
@@ -3429,34 +3438,34 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AB5" s="5">
         <v>30</v>
@@ -3470,34 +3479,34 @@
         <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AC6" s="6">
         <v>40000</v>
@@ -3511,37 +3520,37 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="BC7" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
@@ -3552,34 +3561,34 @@
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AC8" s="6">
         <v>20000</v>
@@ -3593,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E9" s="5">
         <v>1</v>
@@ -3602,25 +3611,25 @@
         <v>4</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AU9" s="5">
         <v>1</v>
@@ -3634,34 +3643,34 @@
         <v>0</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AC10" s="6">
         <v>15000</v>
@@ -3675,34 +3684,34 @@
         <v>0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AB11" s="5">
         <v>50</v>
@@ -3716,37 +3725,37 @@
         <v>1</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA12" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="BC12" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13">
@@ -3757,37 +3766,37 @@
         <v>2</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="BC13" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14">
@@ -3798,34 +3807,34 @@
         <v>0</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AD14" s="6">
         <v>3</v>
@@ -3839,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E15" s="5">
         <v>1</v>
@@ -3848,25 +3857,25 @@
         <v>5</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA15" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AC15" s="5">
         <v>200000</v>
@@ -3880,7 +3889,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E16" s="6">
         <v>1</v>
@@ -3889,32 +3898,32 @@
         <v>15</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AD16" s="6">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:BL16"/>
+  <autoFilter ref="B2:BM16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3931,10 +3940,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C1" s="2"/>
     </row>
@@ -3943,7 +3952,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>6</v>
@@ -3954,10 +3963,10 @@
         <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4">
@@ -3965,7 +3974,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>152</v>
@@ -3981,18 +3990,18 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8">
@@ -4000,15 +4009,15 @@
         <v>167</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -4019,7 +4028,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:BL8"/>
+  <dimension ref="A1:BM8"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.53125" customWidth="1"/>
@@ -4070,15 +4079,15 @@
     <col min="59" max="60" width="23.4375" customWidth="1"/>
     <col min="61" max="61" width="18.75" customWidth="1"/>
     <col min="62" max="63" width="21.09375" customWidth="1"/>
-    <col min="64" max="64" width="22.265625" customWidth="1"/>
+    <col min="64" max="65" width="22.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -4142,6 +4151,7 @@
       <c r="BJ1" s="2"/>
       <c r="BK1" s="2"/>
       <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -4336,43 +4346,46 @@
       <c r="BL2" s="4" t="s">
         <v>235</v>
       </c>
+      <c r="BM2" s="4" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>238</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -4389,7 +4402,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -4428,43 +4441,44 @@
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
+      <c r="BM3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -4481,7 +4495,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -4520,43 +4534,44 @@
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
+      <c r="BM4" s="4"/>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL5" s="5">
         <v>1</v>
@@ -4564,46 +4579,46 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C6" s="6">
         <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AR6" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AT6" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AU6" s="6">
         <v>1</v>
@@ -4617,34 +4632,34 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AD7" s="5">
         <v>3</v>
@@ -4652,50 +4667,50 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C8" s="6">
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AT8" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AU8" s="6">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:BL8"/>
+  <autoFilter ref="B2:BM8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4715,10 +4730,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -4732,7 +4747,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>6</v>
@@ -4741,16 +4756,16 @@
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3">
@@ -4758,22 +4773,22 @@
         <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>125</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>125</v>
@@ -4784,33 +4799,33 @@
         <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>152</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D5" s="5">
         <v>0</v>
@@ -4830,10 +4845,10 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D6" s="6">
         <v>50</v>
@@ -4853,10 +4868,10 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D7" s="5">
         <v>0</v>
@@ -4876,10 +4891,10 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D8" s="6">
         <v>0</v>
@@ -4899,10 +4914,10 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D9" s="5">
         <v>0</v>
